--- a/public/templates/Drivers Import File.xlsx
+++ b/public/templates/Drivers Import File.xlsx
@@ -1,42 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Panashe Ngorima\OneDrive\Desktop\Basilmark Work Files\Gonyeti\Template Files\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C08384-FC3D-45A5-B65E-14295D436048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16DE496B-71F6-4847-A4D7-3256129123A5}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
+  <si>
+    <t>transporter_number</t>
+  </si>
   <si>
     <t>name</t>
   </si>
@@ -104,55 +86,130 @@
     <t>contract_duration</t>
   </si>
   <si>
+    <t>start_date</t>
+  </si>
+  <si>
     <t>expiry_date</t>
   </si>
   <si>
-    <t>start_date</t>
-  </si>
-  <si>
-    <t>transporter_number</t>
+    <t>departments</t>
+  </si>
+  <si>
+    <t>post</t>
+  </si>
+  <si>
+    <t>#FPT00015</t>
+  </si>
+  <si>
+    <t>Tatenda</t>
+  </si>
+  <si>
+    <t>Blessing</t>
+  </si>
+  <si>
+    <t>Chikwanha</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>tatenda.c@example.com</t>
+  </si>
+  <si>
+    <t>+263 77 678 9012</t>
+  </si>
+  <si>
+    <t>63-765432B21</t>
+  </si>
+  <si>
+    <t>123456AB</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>FN123456</t>
+  </si>
+  <si>
+    <t>Zimbabwe</t>
+  </si>
+  <si>
+    <t>Harare</t>
+  </si>
+  <si>
+    <t>Mbare</t>
+  </si>
+  <si>
+    <t>15 Ardbennie Rd</t>
+  </si>
+  <si>
+    <t>Rudo Chikwanha</t>
+  </si>
+  <si>
+    <t>Wife</t>
+  </si>
+  <si>
+    <t>+263 77 111 2222</t>
+  </si>
+  <si>
+    <t>John Banda</t>
+  </si>
+  <si>
+    <t>+263 77 333 4444</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>Driver</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="4">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
+      <b val="0"/>
+      <i val="1"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -165,12 +222,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -179,94 +236,78 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+  <cellXfs count="13">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" fontId="1" numFmtId="14" fillId="2" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" fontId="0" numFmtId="14" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="14" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="3" numFmtId="49" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="164" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -308,7 +349,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -360,7 +401,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -412,7 +453,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -421,236 +462,384 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2446C49F-568E-4E6A-A2D6-7A6B0144A42A}">
-  <dimension ref="A1:Y1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:AA2"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="5" width="22.109375" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" style="8" customWidth="1"/>
-    <col min="7" max="23" width="22.109375" customWidth="1"/>
-    <col min="24" max="25" width="22.109375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="18.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="6.57" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="12.854" bestFit="true" customWidth="true" style="8"/>
+    <col min="7" max="7" width="25.851" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="14.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="5.57" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="18" max="18" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="19" max="19" width="12.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="20" max="20" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="21" max="21" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="22" max="22" width="20.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="23" max="23" width="17.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="24" max="24" width="12.854" bestFit="true" customWidth="true" style="8"/>
+    <col min="25" max="25" width="12.854" bestFit="true" customWidth="true" style="8"/>
+    <col min="26" max="26" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="27" max="27" width="8.141" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" customHeight="1" ht="18.75" s="5" customFormat="1">
       <c r="A1" s="6" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="9" t="s">
         <v>23</v>
       </c>
       <c r="Y1" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
+      <c r="A2" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="11">
+        <v>32217.0</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" s="12">
+        <v>5</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="T2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="W2" s="12">
+        <v>12</v>
+      </c>
+      <c r="X2" s="11">
+        <v>46023.0</v>
+      </c>
+      <c r="Y2" s="11">
+        <v>46387.0</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" r:id="rId1ps"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>